--- a/artfynd/A 44556-2025 artfynd.xlsx
+++ b/artfynd/A 44556-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303152</v>
       </c>
       <c r="B2" t="n">
-        <v>57744</v>
+        <v>57746</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44556-2025 artfynd.xlsx
+++ b/artfynd/A 44556-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303152</v>
       </c>
       <c r="B2" t="n">
-        <v>57746</v>
+        <v>57747</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44556-2025 artfynd.xlsx
+++ b/artfynd/A 44556-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303152</v>
       </c>
       <c r="B2" t="n">
-        <v>57747</v>
+        <v>57748</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44556-2025 artfynd.xlsx
+++ b/artfynd/A 44556-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303152</v>
       </c>
       <c r="B2" t="n">
-        <v>57748</v>
+        <v>57751</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44556-2025 artfynd.xlsx
+++ b/artfynd/A 44556-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303152</v>
       </c>
       <c r="B2" t="n">
-        <v>57751</v>
+        <v>57752</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44556-2025 artfynd.xlsx
+++ b/artfynd/A 44556-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131303152</v>
+        <v>133217962</v>
       </c>
       <c r="B2" t="n">
-        <v>57764</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Baktjärnen, Ång</t>
+          <t>Högkälen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586411</v>
+        <v>586123</v>
       </c>
       <c r="R2" t="n">
-        <v>7010535</v>
+        <v>7010409</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,27 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Observationen är gjord i samband med fågelinventeringar i SvK:s projekt Inlandspaktet.</t>
+          <t>Avbarkningar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,15 +780,228 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131303152</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57813</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100136</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lappuggla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Strix nebulosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Baktjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>586411</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7010535</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Observationen är gjord i samband med fågelinventeringar i SvK:s projekt Inlandspaktet.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Janne Dahlén</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Janne Dahlén</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133406091</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Baktjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>586213</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7010330</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44556-2025 artfynd.xlsx
+++ b/artfynd/A 44556-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133217962</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131303152</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,8 +1017,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133406091</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>